--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C8AB7F-F9D6-4AA2-A2AF-B46381A802B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D89EA98-3C8B-4AC0-815C-3B009D28B93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>James Craven</t>
   </si>
@@ -254,9 +254,6 @@
     <t>Buyside</t>
   </si>
   <si>
-    <t>CSDN-0000007327</t>
-  </si>
-  <si>
     <t>IndustryGroup/HLSector</t>
   </si>
   <si>
@@ -270,6 +267,15 @@
   </si>
   <si>
     <t>VEValidationList</t>
+  </si>
+  <si>
+    <t>CSDN-0000002536</t>
+  </si>
+  <si>
+    <t>Ajay Nair</t>
+  </si>
+  <si>
+    <t>System Administrator</t>
   </si>
 </sst>
 </file>
@@ -319,14 +325,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -610,11 +615,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -631,6 +636,22 @@
       </c>
       <c r="B2" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -640,10 +661,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -652,14 +674,6 @@
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -737,7 +751,7 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>14</v>
@@ -818,7 +832,7 @@
         <v>39</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -828,11 +842,11 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
         <v>41</v>
@@ -913,7 +927,7 @@
         <v>56</v>
       </c>
       <c r="AE2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1006,13 +1020,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>74</v>
+      <c r="A2" s="4" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,18 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D89EA98-3C8B-4AC0-815C-3B009D28B93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2211DF59-74DA-4332-A6AF-C9AD3E1848C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
-    <sheet name="CAOUsers" sheetId="13" r:id="rId2"/>
-    <sheet name="AppName" sheetId="3" r:id="rId3"/>
-    <sheet name="ModuleName" sheetId="4" r:id="rId4"/>
-    <sheet name="AddOpportunity" sheetId="12" r:id="rId5"/>
-    <sheet name="AddContact" sheetId="14" r:id="rId6"/>
-    <sheet name="VEValidationList" sheetId="15" r:id="rId7"/>
+    <sheet name="AppName" sheetId="3" r:id="rId2"/>
+    <sheet name="ModuleName" sheetId="4" r:id="rId3"/>
+    <sheet name="AddOpportunity" sheetId="12" r:id="rId4"/>
+    <sheet name="AddContact" sheetId="14" r:id="rId5"/>
+    <sheet name="VEValidationList" sheetId="15" r:id="rId6"/>
+    <sheet name="NewOpportunityCounterparty" sheetId="16" r:id="rId7"/>
+    <sheet name="FilterSections" sheetId="17" r:id="rId8"/>
+    <sheet name="CounterpartyContact" sheetId="18" r:id="rId9"/>
+    <sheet name="CounterpartyComments" sheetId="19" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="110">
   <si>
     <t>James Craven</t>
   </si>
@@ -276,6 +279,102 @@
   </si>
   <si>
     <t>System Administrator</t>
+  </si>
+  <si>
+    <t>Engagements</t>
+  </si>
+  <si>
+    <t>Companyname</t>
+  </si>
+  <si>
+    <t>Geller &amp; Company</t>
+  </si>
+  <si>
+    <t>Financial</t>
+  </si>
+  <si>
+    <t>FilterSections</t>
+  </si>
+  <si>
+    <t>SubFilters</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Get Companies from existing Company List</t>
+  </si>
+  <si>
+    <t>Company List</t>
+  </si>
+  <si>
+    <t>2022 Summit Attendees</t>
+  </si>
+  <si>
+    <t>Engagement</t>
+  </si>
+  <si>
+    <t>Swiss Alps</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Auto-Test Comments</t>
+  </si>
+  <si>
+    <t>ContactName</t>
+  </si>
+  <si>
+    <t>Alan Test</t>
+  </si>
+  <si>
+    <t>FilterType</t>
+  </si>
+  <si>
+    <t>Industry/Product Focus</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>8K Miles</t>
+  </si>
+  <si>
+    <t>FIG</t>
+  </si>
+  <si>
+    <t>Get Companies from existing Engagement</t>
+  </si>
+  <si>
+    <t>CommentsType</t>
+  </si>
+  <si>
+    <t>CommentsText</t>
+  </si>
+  <si>
+    <t>Administrative</t>
+  </si>
+  <si>
+    <t>Internal</t>
+  </si>
+  <si>
+    <t>Next Steps</t>
+  </si>
+  <si>
+    <t>Administrative Comments</t>
+  </si>
+  <si>
+    <t>Internal Comments</t>
+  </si>
+  <si>
+    <t>External Comments</t>
+  </si>
+  <si>
+    <t>Next Steps Comments</t>
   </si>
 </sst>
 </file>
@@ -325,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -335,6 +434,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,13 +716,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -630,7 +730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -638,7 +738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -646,12 +746,66 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>76</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BDA5E3-E591-4217-B969-32786CE2AACB}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -660,20 +814,21 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FBB8EB1-471A-4668-845A-6810E22F6BA4}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -682,44 +837,26 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -728,19 +865,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -835,7 +972,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -937,22 +1074,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
@@ -978,7 +1115,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -1009,22 +1146,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="83.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="83.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>73</v>
       </c>
@@ -1033,4 +1170,140 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AD5E32-1F75-408B-BF28-CC9346CE869B}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11B5948-2390-457E-837B-ABA1BE0B3211}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E383AB-109B-429A-9662-41F16EFC0EA6}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2211DF59-74DA-4332-A6AF-C9AD3E1848C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30856AC3-3F13-4C4F-A8C3-D73016CBA221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="FilterSections" sheetId="17" r:id="rId8"/>
     <sheet name="CounterpartyContact" sheetId="18" r:id="rId9"/>
     <sheet name="CounterpartyComments" sheetId="19" r:id="rId10"/>
+    <sheet name="EngComments" sheetId="20" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="116">
   <si>
     <t>James Craven</t>
   </si>
@@ -375,6 +376,24 @@
   </si>
   <si>
     <t>Next Steps Comments</t>
+  </si>
+  <si>
+    <t>Kevin Ford</t>
+  </si>
+  <si>
+    <t>Compliance User</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Compliance</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Compliance Comments</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>Next Step</t>
   </si>
 </sst>
 </file>
@@ -715,14 +734,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -730,7 +749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -738,7 +757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -746,12 +765,20 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>76</v>
       </c>
       <c r="B4" t="s">
         <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -761,14 +788,14 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BDA5E3-E591-4217-B969-32786CE2AACB}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>101</v>
       </c>
@@ -776,7 +803,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>103</v>
       </c>
@@ -784,7 +811,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>104</v>
       </c>
@@ -792,7 +819,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -800,12 +827,20 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>105</v>
       </c>
       <c r="B5" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B6" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -813,22 +848,53 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE4B432-C4FF-4884-91C2-898367FA5347}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -836,25 +902,48 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>78</v>
       </c>
@@ -868,16 +957,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -972,7 +1061,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1077,19 +1166,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
@@ -1115,7 +1204,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -1149,19 +1238,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="83.109375" customWidth="1"/>
-    <col min="2" max="2" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="83.140625" customWidth="1"/>
+    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>73</v>
       </c>
@@ -1175,13 +1264,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AD5E32-1F75-408B-BF28-CC9346CE869B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
@@ -1192,7 +1281,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>80</v>
       </c>
@@ -1211,14 +1300,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11B5948-2390-457E-837B-ABA1BE0B3211}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
@@ -1229,7 +1318,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -1240,7 +1329,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>85</v>
       </c>
@@ -1259,13 +1348,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E383AB-109B-429A-9662-41F16EFC0EA6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>92</v>
       </c>
@@ -1276,7 +1365,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>93</v>
       </c>
@@ -1287,7 +1376,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>95</v>
       </c>
@@ -1295,7 +1384,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>96</v>
       </c>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30856AC3-3F13-4C4F-A8C3-D73016CBA221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D90131-A383-4B20-B2EA-BDECFA3423BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="CounterpartyContact" sheetId="18" r:id="rId9"/>
     <sheet name="CounterpartyComments" sheetId="19" r:id="rId10"/>
     <sheet name="EngComments" sheetId="20" r:id="rId11"/>
+    <sheet name="FullReqEng" sheetId="21" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="117">
   <si>
     <t>James Craven</t>
   </si>
@@ -394,6 +395,9 @@
   </si>
   <si>
     <t>Next Step</t>
+  </si>
+  <si>
+    <t>Billing Contact is required - review engagement contacts or add CF engagement Contact at the top of the page.Primary Contact is required - review engagement contacts or add CF engagement Contact at the top of the page.A Conflicts Check was completed more than 30 days ago - a new Conflicts Check must be completed.</t>
   </si>
 </sst>
 </file>
@@ -443,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -454,6 +458,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,6 +909,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C44B9E-4C84-4780-B625-147466BEF9C9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
@@ -1237,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="83.140625" customWidth="1"/>
@@ -1253,6 +1269,11 @@
     <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D90131-A383-4B20-B2EA-BDECFA3423BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3B3017-751C-4426-89FE-2D01E99D62B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="118">
   <si>
     <t>James Craven</t>
   </si>
@@ -397,7 +397,10 @@
     <t>Next Step</t>
   </si>
   <si>
-    <t>Billing Contact is required - review engagement contacts or add CF engagement Contact at the top of the page.Primary Contact is required - review engagement contacts or add CF engagement Contact at the top of the page.A Conflicts Check was completed more than 30 days ago - a new Conflicts Check must be completed.</t>
+    <t>Billing Contact is required - review engagement contacts or add CF engagement Contact at the top of the page.Primary Contact is required - review engagement contacts or add CF engagement Contact at the top of the page.</t>
+  </si>
+  <si>
+    <t>*Shared Services Expense*Expense Cap*Legal Cap*Indemnification Language*Retainer*Progress/Monthly Fee*Contingent Fee*Tail Expires*Confidentiality Agreement*Fairness Opinion Component*Date Engaged</t>
   </si>
 </sst>
 </file>
@@ -1253,11 +1256,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="83.140625" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1271,9 +1274,15 @@
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>116</v>
+      </c>
+      <c r="B3" s="4"/>
+    </row>
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3B3017-751C-4426-89FE-2D01E99D62B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44078AE8-37F8-4ACB-A80F-642B94CA2FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44078AE8-37F8-4ACB-A80F-642B94CA2FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174EF758-625C-45C9-9EB1-D770734F228D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174EF758-625C-45C9-9EB1-D770734F228D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C9A2DA-5B06-439F-8504-969D347CAEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="117">
   <si>
     <t>James Craven</t>
   </si>
@@ -253,9 +253,6 @@
     <t>Sonika Goyal</t>
   </si>
   <si>
-    <t>Kristian M. Whalen</t>
-  </si>
-  <si>
     <t>Buyside</t>
   </si>
   <si>
@@ -274,9 +271,6 @@
     <t>VEValidationList</t>
   </si>
   <si>
-    <t>CSDN-0000002536</t>
-  </si>
-  <si>
     <t>Ajay Nair</t>
   </si>
   <si>
@@ -401,6 +395,9 @@
   </si>
   <si>
     <t>*Shared Services Expense*Expense Cap*Legal Cap*Indemnification Language*Retainer*Progress/Monthly Fee*Contingent Fee*Tail Expires*Confidentiality Agreement*Fairness Opinion Component*Date Engaged</t>
+  </si>
+  <si>
+    <t>CSDN-0000006544</t>
   </si>
 </sst>
 </file>
@@ -777,18 +774,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -807,26 +804,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -834,23 +831,23 @@
         <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -869,42 +866,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -964,7 +961,7 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +993,7 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>14</v>
@@ -1077,7 +1074,7 @@
         <v>39</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -1088,10 +1085,10 @@
         <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
         <v>41</v>
@@ -1172,7 +1169,7 @@
         <v>56</v>
       </c>
       <c r="AE2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1240,13 +1237,13 @@
         <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1265,24 +1262,24 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1302,24 +1299,24 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1339,35 +1336,35 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
         <v>85</v>
-      </c>
-      <c r="B3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1386,40 +1383,40 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C9A2DA-5B06-439F-8504-969D347CAEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1C0ABF-04DD-4397-B2BB-CC5417533342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="117">
   <si>
     <t>James Craven</t>
   </si>
@@ -1181,10 +1181,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -1236,14 +1236,22 @@
       <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
-        <v>67</v>
-      </c>
       <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>91</v>
+      </c>
+      <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F1C0ABF-04DD-4397-B2BB-CC5417533342}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B217FC-7A7A-4A3C-89D4-09D07E484C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
   <si>
     <t>James Craven</t>
   </si>
@@ -361,18 +361,6 @@
     <t>Next Steps</t>
   </si>
   <si>
-    <t>Administrative Comments</t>
-  </si>
-  <si>
-    <t>Internal Comments</t>
-  </si>
-  <si>
-    <t>External Comments</t>
-  </si>
-  <si>
-    <t>Next Steps Comments</t>
-  </si>
-  <si>
     <t>Kevin Ford</t>
   </si>
   <si>
@@ -382,9 +370,6 @@
     <t xml:space="preserve"> Compliance</t>
   </si>
   <si>
-    <t xml:space="preserve"> Compliance Comments</t>
-  </si>
-  <si>
     <t>Compliance</t>
   </si>
   <si>
@@ -398,6 +383,33 @@
   </si>
   <si>
     <t>CSDN-0000006544</t>
+  </si>
+  <si>
+    <t>Administrative Counterparty Comments</t>
+  </si>
+  <si>
+    <t>Internal Counterparty Comments</t>
+  </si>
+  <si>
+    <t>External Counterparty Comments</t>
+  </si>
+  <si>
+    <t>Next Steps Counterparty Comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Compliance Counterparty Comments</t>
+  </si>
+  <si>
+    <t>Administrative Eng Comments</t>
+  </si>
+  <si>
+    <t>Internal Eng Comments</t>
+  </si>
+  <si>
+    <t>Next Steps Eng Comments</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Compliance Eng Comments</t>
   </si>
 </sst>
 </file>
@@ -782,10 +794,10 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -799,7 +811,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -815,7 +827,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -823,7 +835,7 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -831,7 +843,7 @@
         <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -839,15 +851,15 @@
         <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -877,7 +889,7 @@
         <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -885,23 +897,23 @@
         <v>102</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -1088,7 +1100,7 @@
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E2" t="s">
         <v>41</v>
@@ -1281,13 +1293,13 @@
     </row>
     <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B217FC-7A7A-4A3C-89D4-09D07E484C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64FD385-6287-4BEE-817C-44FFAAE0E922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="7" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -22,9 +22,10 @@
     <sheet name="NewOpportunityCounterparty" sheetId="16" r:id="rId7"/>
     <sheet name="FilterSections" sheetId="17" r:id="rId8"/>
     <sheet name="CounterpartyContact" sheetId="18" r:id="rId9"/>
-    <sheet name="CounterpartyComments" sheetId="19" r:id="rId10"/>
-    <sheet name="EngComments" sheetId="20" r:id="rId11"/>
-    <sheet name="FullReqEng" sheetId="21" r:id="rId12"/>
+    <sheet name="EngComments" sheetId="20" r:id="rId10"/>
+    <sheet name="OppComments" sheetId="22" r:id="rId11"/>
+    <sheet name="CounterpartyComments" sheetId="19" r:id="rId12"/>
+    <sheet name="FullReqEng" sheetId="21" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="127">
   <si>
     <t>James Craven</t>
   </si>
@@ -250,9 +251,6 @@
     <t>External</t>
   </si>
   <si>
-    <t>Sonika Goyal</t>
-  </si>
-  <si>
     <t>Buyside</t>
   </si>
   <si>
@@ -367,9 +365,6 @@
     <t>Compliance User</t>
   </si>
   <si>
-    <t xml:space="preserve"> Compliance</t>
-  </si>
-  <si>
     <t>Compliance</t>
   </si>
   <si>
@@ -397,9 +392,6 @@
     <t>Next Steps Counterparty Comments</t>
   </si>
   <si>
-    <t xml:space="preserve"> Compliance Counterparty Comments</t>
-  </si>
-  <si>
     <t>Administrative Eng Comments</t>
   </si>
   <si>
@@ -409,7 +401,34 @@
     <t>Next Steps Eng Comments</t>
   </si>
   <si>
-    <t xml:space="preserve"> Compliance Eng Comments</t>
+    <t>Compliance Eng Comments</t>
+  </si>
+  <si>
+    <t>Vijay Kumar</t>
+  </si>
+  <si>
+    <t>Opportunity cannot be updated after engagement creation</t>
+  </si>
+  <si>
+    <t>Administrative Opp Comments</t>
+  </si>
+  <si>
+    <t>Internal Opp Comments</t>
+  </si>
+  <si>
+    <t>Next Steps Opp Comments</t>
+  </si>
+  <si>
+    <t>Compliance Opp Comments</t>
+  </si>
+  <si>
+    <t>Opportunity</t>
+  </si>
+  <si>
+    <t>Get Companies from existing Opportunity</t>
+  </si>
+  <si>
+    <t>Project Deep Dive</t>
   </si>
 </sst>
 </file>
@@ -754,13 +773,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -768,7 +787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -776,7 +795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -784,20 +803,20 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" t="s">
         <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -806,60 +825,52 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BDA5E3-E591-4217-B969-32786CE2AACB}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE4B432-C4FF-4884-91C2-898367FA5347}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>101</v>
       </c>
-      <c r="B2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
       <c r="B3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -868,52 +879,52 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE4B432-C4FF-4884-91C2-898367FA5347}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8597CD50-2CF5-4D19-B893-73DF6C8A5B5E}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>101</v>
       </c>
-      <c r="B2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>102</v>
-      </c>
       <c r="B3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -922,9 +933,63 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BDA5E3-E591-4217-B969-32786CE2AACB}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C44B9E-4C84-4780-B625-147466BEF9C9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -933,17 +998,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -956,24 +1021,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -985,16 +1050,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1005,7 +1070,7 @@
         <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>14</v>
@@ -1086,10 +1151,10 @@
         <v>39</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1097,10 +1162,10 @@
         <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>41</v>
@@ -1181,7 +1246,7 @@
         <v>56</v>
       </c>
       <c r="AE2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1194,19 +1259,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
@@ -1232,9 +1297,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="B2" t="s">
         <v>64</v>
@@ -1252,9 +1317,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -1273,33 +1338,38 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="83.140625" customWidth="1"/>
-    <col min="2" max="2" width="80.28515625" customWidth="1"/>
+    <col min="1" max="1" width="83.109375" customWidth="1"/>
+    <col min="2" max="2" width="80.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1311,32 +1381,32 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AD5E32-1F75-408B-BF28-CC9346CE869B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" t="s">
         <v>88</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1346,45 +1416,75 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11B5948-2390-457E-837B-ABA1BE0B3211}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>83</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>84</v>
       </c>
-      <c r="C3" t="s">
-        <v>85</v>
+      <c r="D3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1395,48 +1495,48 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E383AB-109B-429A-9662-41F16EFC0EA6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
         <v>93</v>
       </c>
-      <c r="C3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>94</v>
-      </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64FD385-6287-4BEE-817C-44FFAAE0E922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED23396D-F43B-4D71-8C5E-B156FDD538EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -773,13 +773,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -787,7 +787,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -795,7 +795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -803,7 +803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -811,7 +811,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>103</v>
       </c>
@@ -827,13 +827,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE4B432-C4FF-4884-91C2-898367FA5347}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
@@ -841,7 +841,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -849,7 +849,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -857,7 +857,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>106</v>
       </c>
@@ -865,7 +865,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -881,13 +881,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8597CD50-2CF5-4D19-B893-73DF6C8A5B5E}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
@@ -895,7 +895,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -903,7 +903,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -911,7 +911,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>106</v>
       </c>
@@ -919,7 +919,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -935,13 +935,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BDA5E3-E591-4217-B969-32786CE2AACB}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>98</v>
       </c>
@@ -949,7 +949,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>100</v>
       </c>
@@ -957,7 +957,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>101</v>
       </c>
@@ -965,7 +965,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>66</v>
       </c>
@@ -973,7 +973,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -989,7 +989,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C44B9E-4C84-4780-B625-147466BEF9C9}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -998,17 +998,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1021,22 +1021,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -1050,16 +1050,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1259,19 +1259,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>57</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>118</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>90</v>
       </c>
@@ -1339,35 +1339,35 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="83.109375" customWidth="1"/>
-    <col min="2" max="2" width="80.33203125" customWidth="1"/>
+    <col min="1" max="1" width="83.140625" customWidth="1"/>
+    <col min="2" max="2" width="80.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="96" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>107</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>119</v>
       </c>
@@ -1381,13 +1381,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AD5E32-1F75-408B-BF28-CC9346CE869B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>76</v>
       </c>
@@ -1398,7 +1398,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>77</v>
       </c>
@@ -1417,17 +1417,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11B5948-2390-457E-837B-ABA1BE0B3211}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>79</v>
       </c>
@@ -1447,7 +1447,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>97</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>82</v>
       </c>
@@ -1495,13 +1495,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E383AB-109B-429A-9662-41F16EFC0EA6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>89</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>90</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>92</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>93</v>
       </c>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F0DBEC-0552-41CE-9A35-4FCEAAF34FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B0871F-CD64-49E3-B32C-645E7A346AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" firstSheet="7" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -428,10 +428,10 @@
     <t>*Shared Services Expense*Expense Cap*Legal Cap*Indemnification Language*Retainer*Progress/Monthly Fee*Contingent Fee*Confidentiality Agreement*Fairness Opinion Component*Date Engaged</t>
   </si>
   <si>
-    <t>Brian Miller</t>
-  </si>
-  <si>
     <t>Sonika Goyal</t>
+  </si>
+  <si>
+    <t>Jennie Stewart</t>
   </si>
 </sst>
 </file>
@@ -776,13 +776,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -798,15 +798,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -814,7 +814,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -830,13 +830,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE4B432-C4FF-4884-91C2-898367FA5347}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -844,7 +844,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -852,7 +852,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -860,7 +860,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -868,7 +868,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -884,13 +884,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8597CD50-2CF5-4D19-B893-73DF6C8A5B5E}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -898,7 +898,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -906,7 +906,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -914,7 +914,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -922,7 +922,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -938,13 +938,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BDA5E3-E591-4217-B969-32786CE2AACB}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -952,7 +952,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -960,7 +960,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -968,7 +968,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -976,7 +976,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>101</v>
       </c>
@@ -992,19 +992,19 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C44B9E-4C84-4780-B625-147466BEF9C9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1015,17 +1015,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1038,22 +1038,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -1067,16 +1067,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1276,19 +1276,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1356,35 +1356,35 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="84.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.28515625" customWidth="1"/>
+    <col min="1" max="1" width="84.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>106</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -1398,13 +1398,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AD5E32-1F75-408B-BF28-CC9346CE869B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1434,17 +1434,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11B5948-2390-457E-837B-ABA1BE0B3211}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -1512,13 +1512,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E383AB-109B-429A-9662-41F16EFC0EA6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>91</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>92</v>
       </c>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B0871F-CD64-49E3-B32C-645E7A346AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC289D49-EB6D-481C-B976-8BDFD02EC9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -776,13 +776,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -790,7 +790,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -798,7 +798,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>127</v>
       </c>
@@ -806,7 +806,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -814,7 +814,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -830,13 +830,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE4B432-C4FF-4884-91C2-898367FA5347}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -844,7 +844,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -852,7 +852,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -860,7 +860,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -868,7 +868,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -884,13 +884,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8597CD50-2CF5-4D19-B893-73DF6C8A5B5E}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -898,7 +898,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -906,7 +906,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -914,7 +914,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>105</v>
       </c>
@@ -922,7 +922,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>104</v>
       </c>
@@ -938,13 +938,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68BDA5E3-E591-4217-B969-32786CE2AACB}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
@@ -952,7 +952,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>99</v>
       </c>
@@ -960,7 +960,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>100</v>
       </c>
@@ -968,7 +968,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>65</v>
       </c>
@@ -976,7 +976,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>101</v>
       </c>
@@ -992,17 +992,17 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C44B9E-4C84-4780-B625-147466BEF9C9}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>126</v>
       </c>
@@ -1015,17 +1015,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0293C6CF-D2AF-4FB5-B989-23A4E6860FD2}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1038,22 +1038,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D296AE2-31EA-40C7-99FB-9B7E70535054}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
@@ -1067,16 +1067,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFD13242-055E-41A8-80D8-6F50F1B57F7C}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>10</v>
       </c>
@@ -1171,7 +1171,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1276,19 +1276,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F2CDCD2-7F5E-40FD-BAB3-4BCEC31CD21E}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>56</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>115</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -1356,35 +1356,35 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="84.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="80.33203125" customWidth="1"/>
+    <col min="1" max="1" width="84.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="80.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>106</v>
       </c>
       <c r="B3" s="4"/>
     </row>
-    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
       </c>
@@ -1398,13 +1398,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1AD5E32-1F75-408B-BF28-CC9346CE869B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1434,17 +1434,17 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D11B5948-2390-457E-837B-ABA1BE0B3211}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>78</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>96</v>
       </c>
@@ -1484,7 +1484,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>81</v>
       </c>
@@ -1512,13 +1512,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38E383AB-109B-429A-9662-41F16EFC0EA6}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>88</v>
       </c>
@@ -1529,7 +1529,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>89</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>91</v>
       </c>
@@ -1548,7 +1548,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>92</v>
       </c>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC289D49-EB6D-481C-B976-8BDFD02EC9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88635AED-86C9-47A0-AB47-454ED786C35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="131">
   <si>
     <t>James Craven</t>
   </si>
@@ -432,6 +432,15 @@
   </si>
   <si>
     <t>Jennie Stewart</t>
+  </si>
+  <si>
+    <t>Info--&gt;Administration: Location where Benefit is to be Provided is required.</t>
+  </si>
+  <si>
+    <t>Benefit is likely &lt;25% outside the US</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location where Benefit </t>
   </si>
 </sst>
 </file>
@@ -1355,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F2386AE-B180-4489-BA71-14068DFEFD5A}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="84.28515625" bestFit="1" customWidth="1"/>
@@ -1366,7 +1375,9 @@
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -1387,6 +1398,14 @@
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88635AED-86C9-47A0-AB47-454ED786C35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68C567F-2D88-4A18-B934-A9AA3BCB5F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="548" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68C567F-2D88-4A18-B934-A9AA3BCB5F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948667A8-9AE9-4199-8559-AED29B582E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" tabRatio="548" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="132">
   <si>
     <t>James Craven</t>
   </si>
@@ -431,9 +431,6 @@
     <t>Sonika Goyal</t>
   </si>
   <si>
-    <t>Jennie Stewart</t>
-  </si>
-  <si>
     <t>Info--&gt;Administration: Location where Benefit is to be Provided is required.</t>
   </si>
   <si>
@@ -441,6 +438,12 @@
   </si>
   <si>
     <t xml:space="preserve">Location where Benefit </t>
+  </si>
+  <si>
+    <t>Christopher Wout</t>
+  </si>
+  <si>
+    <t>CF M&amp;A CAO</t>
   </si>
 </sst>
 </file>
@@ -784,14 +787,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -799,7 +803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -807,15 +811,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -823,7 +830,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -1376,7 +1383,7 @@
         <v>71</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -1402,10 +1409,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" t="s">
         <v>128</v>
-      </c>
-      <c r="B6" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
+++ b/TestData/LV_TMTT0041159_VerifiyTheFunctionalityOfVerballyEngagedCFEngagement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948667A8-9AE9-4199-8559-AED29B582E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A56659-0071-442D-8217-65C0B05595AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="134">
   <si>
     <t>James Craven</t>
   </si>
@@ -444,6 +444,12 @@
   </si>
   <si>
     <t>CF M&amp;A CAO</t>
+  </si>
+  <si>
+    <t>Justin Abelow</t>
+  </si>
+  <si>
+    <t>FS Admin_L</t>
   </si>
 </sst>
 </file>
@@ -787,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
@@ -836,6 +842,14 @@
       </c>
       <c r="B5" t="s">
         <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
